--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -613,17 +613,17 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>محطة / نهضة مصر</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>سائق معدات ثقيلة</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -711,17 +711,17 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>الصف</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>الصباغة وطباعة المنسوجات</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -809,17 +809,17 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة/ فيوتشر</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>الملابس الجاهزة</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -907,17 +907,17 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة / الراعى الصالح</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>سائق معدات ثقيلة</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>مركز الأسمرات</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>صيانة ماكينات الطباعة</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>أمان سيفتى</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>فني الأنظمة المدمجة والذكاء الاصطناعي</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة / ابو زعبل للأسمدة</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>تصنيع الاسطمبات</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>المنيا</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>برمجة الحاسب الآلي</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>محطة / المستقبل ( 2 )</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>تشغيل وصيانة معدات الغزل</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>محطة / نهضة مصر</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>صيانة الهواتف المحمولة</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
@@ -1593,17 +1593,17 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>الألات الدقيقة بالقاهرة</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>تشكيل المعادن وتصنيع الحلي</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>شبرا للصناعات النسيجية والهندسية</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>تشغيل معدات الصيد والملاحة والفنون البحرية</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>الصيد</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>مشترك المظلات</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>تشغيل المخارط المبرمجة بالحاسب CNC</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة / هاردوير</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>فنى تجهيز خامات التعدين</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>المنيا</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>فني البترول والبتروكيماويات</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الصناعات البتروكيماوية</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الاميرية</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>الأميرية التجريبى</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>تشكيل المعادن وتصنيع الحلي</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L17" s="7" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>محطة / طيبة تكنولوجى</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>صيانة واصلاح الأجهزة المكتبية الإلكترونية</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L18" s="7" t="n">
@@ -2279,17 +2279,17 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>الصف</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>تشغيل ماكينات تصنيع البلاستيك</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الصناعات البتروكيماوية</t>
         </is>
       </c>
       <c r="L19" s="7" t="n">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>الشروق ( حدائق الاهرام )</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>نجارة عامة</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>النجارة</t>
         </is>
       </c>
       <c r="L20" s="7" t="n">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>مجمع الحوامدية</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>فني الأنظمة المدمجة والذكاء الاصطناعي</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -2573,17 +2573,17 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>الشركة الدولية لتصنيع الملابس الجاهزة</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>برمجة الحاسب الآلي</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L22" s="7" t="n">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>المصرية للحاسبات ( فرع المعادى )</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>البرادة العامة</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -2769,17 +2769,17 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>الشركة الدولية لتصنيع الملابس الجاهزة</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>فني البرمجيات والتطبيقات الصناعية</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>سيارات امبابة</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>التطريز اليدوي</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>منتجات حرف يدوية</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة / الباشا</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>صيانة ماكينات حياكة الملابس</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>الألات الدقيقة بالقاهرة</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>البرادة العامة</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>محطة / الصانع الأول</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>برمجة الحاسب الآلي</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة / ادفانس</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهرباء الصناعية</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L29" s="7" t="n">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>كوم أوشيم - الفيوم</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>الكهرباء</t>
+          <t>صيانة واصلاح اجهزة التبريد وتكييف الهواء</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>محطة / الباشا</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>فني بصريات</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L31" s="7" t="n">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>محطة / المصرية للحاسبات بشبرا الخيمة</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>نجارة عامة</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>النجارة</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -3651,17 +3651,17 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>الشركة العالمية لصناعة الملابس ( تيد لاموند )</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>تشغيل وصيانة أنظمة وشبكات الحاسب</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L33" s="7" t="n">
@@ -3749,17 +3749,17 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة/ النبأ الوطنى للنشر</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>تشغيل معدات الصيد والملاحة والفنون البحرية</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الصيد</t>
         </is>
       </c>
       <c r="L34" s="7" t="n">
@@ -3847,17 +3847,17 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>محطة / أم أف سى</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>الإلكترونيات الصناعية</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L35" s="7" t="n">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>المنيا</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>تشكيل الزجاج</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>منتجات حرف يدوية</t>
         </is>
       </c>
       <c r="L36" s="7" t="n">
@@ -4043,17 +4043,17 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>الشروق ( حدائق الاهرام )</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>فني تشغيل وصيانة الطلمبات والضواغط</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L37" s="7" t="n">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة / الياسمينا للملابس الجاهزة</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>الكهرباء</t>
+          <t>تشغيل وصيانة أنظمة وشبكات الحاسب</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L38" s="7" t="n">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>شبرا للصناعات النسيجية والهندسية</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>الصباغة وطباعة المنسوجات</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L39" s="7" t="n">
@@ -4337,17 +4337,17 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>كوم أوشيم - الفيوم</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>فني النقل البحري والملاحة</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>بحرية</t>
         </is>
       </c>
       <c r="L40" s="7" t="n">
@@ -4435,17 +4435,17 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>محطة/ دار التعاون للطباعة</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>صيانة واصلاح الأجهزة المسموعة والمرئية</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L41" s="7" t="n">
@@ -4533,17 +4533,17 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>جنوب الصعيد</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>مركز الأسمرات</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>ماكينات الورش</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L42" s="7" t="n">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>منيل شيحة</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>نجارة عامة</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>النجارة</t>
         </is>
       </c>
       <c r="L43" s="7" t="n">
@@ -4729,17 +4729,17 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>مجموعة الأسكندرية الصناعية ( فرع كرداسة )</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>فني تشغيل وصيانة الطلمبات والضواغط</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L44" s="7" t="n">
@@ -4827,17 +4827,17 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>مشترك العباسية</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>فني النقل البحري والملاحة</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>بحرية</t>
         </is>
       </c>
       <c r="L45" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>منيل شيحة</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>تصميم الجرافيك وبرمجة مواقع الانترنت</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L46" s="7" t="n">
@@ -5023,17 +5023,17 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>أمان سيفتى</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>صيانة السيارات</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>المركبات</t>
         </is>
       </c>
       <c r="L47" s="7" t="n">
@@ -5121,17 +5121,17 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>المنيا</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>صيانة وإصلاح الأجهزة الطبية</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L48" s="7" t="n">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>سيارات امبابة</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>تشغيل وصيانة أنظمة وشبكات الحاسب</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L49" s="7" t="n">
@@ -5317,17 +5317,17 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>دار الرحمن</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>تشغيل وصيانة معدات الغزل</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L50" s="7" t="n">
@@ -5415,17 +5415,17 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>الشركة الدولية لتصنيع الملابس الجاهزة</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>الكهرباء</t>
+          <t>صيانة ماكينات الطباعة</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L51" s="7" t="n">
@@ -5513,17 +5513,17 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>مجمع الحوامدية</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>فني النقل البحري والملاحة</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>بحرية</t>
         </is>
       </c>
       <c r="L52" s="7" t="n">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>الألات الدقيقة بالقاهرة</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>الكهرباء</t>
+          <t>الطاقة المتجددة (الكهروضوئية)</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L53" s="7" t="n">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة / الفارس</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>صيانة واصلاح الأجهزة المكتبية الإلكترونية</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L54" s="7" t="n">
@@ -5807,17 +5807,17 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>الشروق ( حدائق الاهرام )</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>صيانة واصلاح الأجهزة المكتبية الإلكترونية</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L55" s="7" t="n">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>كوم أوشيم - الفيوم</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>برمجة الحاسب الآلي</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L56" s="7" t="n">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>الكمال ترند لينك</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>تمديدات شبكات المواسير الصناعية والصحية</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L57" s="7" t="n">
@@ -6101,17 +6101,17 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>الشركة العالمية لصناعة الملابس ( تيد لاموند )</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>نجارة عامة</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>النجارة</t>
         </is>
       </c>
       <c r="L58" s="7" t="n">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>بايونيرز الدولية للحاسبات ( 2 )</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>الصيانة الميكانيكية</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -6297,17 +6297,17 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>مصنع سمارت للتطوير ( بندر ملوى )</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>طباعة الأوفست</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>الطباعة</t>
         </is>
       </c>
       <c r="L60" s="7" t="n">
@@ -6395,17 +6395,17 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>محطة/ دار التعاون للطباعة</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>مساعد فني معمل كيماوي</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>الكيميائية</t>
         </is>
       </c>
       <c r="L61" s="7" t="n">
@@ -6493,17 +6493,17 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>محطة / نت سكيل1</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>اصلاح ودهان هياكل السيارات</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المركبات</t>
         </is>
       </c>
       <c r="L62" s="7" t="n">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>معادن و سيارات وادى حوف</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهرباء الصناعية</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L63" s="7" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>محطة/ فيوتشر</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>تشغيل المخارط المبرمجة بالحاسب CNC</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L64" s="7" t="n">
@@ -6787,17 +6787,17 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>منيل شيحة</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>تشغيل وصيانة المحركات البحرية</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L65" s="7" t="n">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>الصف</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>صيانة ماكينات حياكة الملابس</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>بايونيرز الدولية للحاسبات ( 2 )</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>سائق معدات ثقيلة</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L67" s="7" t="n">
@@ -7081,17 +7081,17 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة / نت سكيل2</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>الكهرباء</t>
+          <t>فني بصريات</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -7179,17 +7179,17 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة / المستقبل ( 2 )</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>اصلاح ودهان هياكل السيارات</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>المركبات</t>
         </is>
       </c>
       <c r="L69" s="7" t="n">
@@ -7277,17 +7277,17 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>الألات الدقيقة بالقاهرة</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>صيانة واصلاح اجهزة التبريد وتكييف الهواء</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L70" s="7" t="n">
@@ -7375,17 +7375,17 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>محطة / المطرية</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>التطريز اليدوي</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>منتجات حرف يدوية</t>
         </is>
       </c>
       <c r="L71" s="7" t="n">
@@ -7473,17 +7473,17 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>مجموعة الأسكندرية الصناعية ( فرع حدائق الأهرام )</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>صيانة واصلاح الأجهزة المكتبية الإلكترونية</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L72" s="7" t="n">
@@ -7571,17 +7571,17 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>بايونيرز الدولية للحاسبات ( 2 )</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>الصباغة وطباعة المنسوجات</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L73" s="7" t="n">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الاميرية</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>الأميرية التجريبى</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>صيانة واصلاح اجهزة التبريد وتكييف الهواء</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L74" s="7" t="n">
@@ -7767,17 +7767,17 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة/ النبأ الوطنى للنشر</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>تشغيل الفرايز المبرمجة بالحاسب CNC</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L75" s="7" t="n">
@@ -7865,17 +7865,17 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الاميرية</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>الأميرية التجريبى</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>فني الأنظمة المدمجة والذكاء الاصطناعي</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L76" s="7" t="n">
@@ -7963,17 +7963,17 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>معادن وتبريد شبرا</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>اصلاح ودهان هياكل السيارات</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>المركبات</t>
         </is>
       </c>
       <c r="L77" s="7" t="n">
@@ -8061,17 +8061,17 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>محطة/ الفنية الحديثة للطباعة</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>تشغيل وصيانة المحركات البحرية</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L78" s="7" t="n">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>المصرية للحاسبات ( فرع المعادى )</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>صيانة واصلاح الأجهزة المسموعة والمرئية</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L79" s="7" t="n">
@@ -8257,17 +8257,17 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>مشترك العباسية</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>تشغيل معدات الصيد والملاحة والفنون البحرية</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>الصيد</t>
         </is>
       </c>
       <c r="L80" s="7" t="n">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة / الفارس</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>تصميم الجرافيك وبرمجة مواقع الانترنت</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L81" s="7" t="n">
@@ -8453,17 +8453,17 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>مشترك الإسكندرية</t>
+          <t>صيانة السيارات بشبرا</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>تشغيل الفرايز المبرمجة بالحاسب CNC</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L82" s="7" t="n">
@@ -8551,17 +8551,17 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>مركز الأسمرات</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>فني تشغيل وصيانة الطلمبات والضواغط</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L83" s="7" t="n">
@@ -8649,17 +8649,17 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>محطة / نت سكيل2</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>صيانة واصلاح الأجهزة المكتبية الإلكترونية</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L84" s="7" t="n">
@@ -8747,17 +8747,17 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>بنى سويف</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الإلكترونيات الصناعية</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L85" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>طباعة امبابة</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>اللحام</t>
+          <t>سائق معدات ثقيلة</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>التعدين</t>
         </is>
       </c>
       <c r="L86" s="7" t="n">
@@ -8943,17 +8943,17 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>محطة / النصر للمسبوكات</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>فني البرمجيات والتطبيقات الصناعية</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>الكهربائية</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L87" s="7" t="n">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>محطة / المستقبل ( 2 )</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>صيانة ماكينات حياكة الملابس</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -9139,17 +9139,17 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>الألات الدقيقة بالقاهرة</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>صيانة واصلاح اجهزة التبريد وتكييف الهواء</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L89" s="7" t="n">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>شمال الصعيد</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>مصنع سمارت للتطوير ( المنيا أبو فيلو )</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>الكهرباء</t>
+          <t>صيانة واصلاح اجهزة التبريد وتكييف الهواء</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L90" s="7" t="n">
@@ -9335,17 +9335,17 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>مشترك العباسية</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>الكهرباء الصناعية</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L91" s="7" t="n">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>الدلتا</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>مشترك القاهرة</t>
+          <t>محطة / الباشا</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>النجارة</t>
+          <t>صيانة الهواتف المحمولة</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L92" s="7" t="n">
@@ -9531,17 +9531,17 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>القنال</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>مركز الأسمرات</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>التبريد والتكييف</t>
+          <t>الكهرباء الصناعية</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>المعدنية والميكانيكية</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L93" s="7" t="n">
@@ -9629,17 +9629,17 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>شمال الصعيد</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>مشترك اسوان</t>
+          <t>معادن و سيارات وادى حوف</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>فني البترول والبتروكيماويات</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الصناعات البتروكيماوية</t>
         </is>
       </c>
       <c r="L94" s="7" t="n">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>محطة / نت سكيل2</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>صيانة ماكينات حياكة الملابس</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L95" s="7" t="n">
@@ -9825,17 +9825,17 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>شمال القاهرة</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>شبرا للصناعات النسيجية والهندسية</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>تشكيل الزجاج</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>منتجات حرف يدوية</t>
         </is>
       </c>
       <c r="L96" s="7" t="n">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>مشترك سوهاج</t>
+          <t>الكمال ترند لينك</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>خراطة المعادن</t>
+          <t>تشغيل الفرايز المبرمجة بالحاسب CNC</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L97" s="7" t="n">
@@ -10021,17 +10021,17 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>الساحل الشمالي</t>
+          <t>جنوب القاهرة</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>طرة الأسمنت</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>الإلكترونيات الصناعية</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>البناء والتشييد</t>
+          <t>الكهربية والإلكترونية</t>
         </is>
       </c>
       <c r="L98" s="7" t="n">
@@ -10119,17 +10119,17 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>القاهرة الكبرى</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>مشترك الجيزة</t>
+          <t>بايونيرز الدولية للحاسبات ( 2 )</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>تشغيل وصيانة معدات الغزل</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>الغزل والنسيج</t>
         </is>
       </c>
       <c r="L99" s="7" t="n">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>مشترك المنيا</t>
+          <t>الصف</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>الميكانيكا</t>
+          <t>فني البرمجيات والتطبيقات الصناعية</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>الزراعة</t>
+          <t>تكنولوجيا المعلومات</t>
         </is>
       </c>
       <c r="L100" s="7" t="n">
@@ -10315,17 +10315,17 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>مشترك أسيوط</t>
+          <t>سيارات امبابة</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>البناء</t>
+          <t>ماكينات الورش</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>الإلكترونيات</t>
+          <t>المعدنية والميكانيكية</t>
         </is>
       </c>
       <c r="L101" s="7" t="n">
